--- a/data/open-pos.xlsx
+++ b/data/open-pos.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1733" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="323">
   <si>
     <t>Account</t>
   </si>
@@ -287,9 +287,6 @@
     <t>5616</t>
   </si>
   <si>
-    <t>PPE-GLOVES</t>
-  </si>
-  <si>
     <t>CASCO INDUSTRIES, INC</t>
   </si>
   <si>
@@ -401,6 +398,21 @@
     <t>ESTIMATED FREIGHT</t>
   </si>
   <si>
+    <t>RAGTOP FIRE HELMETS AND RESTO</t>
+  </si>
+  <si>
+    <t>SMALL</t>
+  </si>
+  <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
+    <t>LARGE</t>
+  </si>
+  <si>
+    <t>2XL</t>
+  </si>
+  <si>
     <t>100-30-350-5352-</t>
   </si>
   <si>
@@ -725,6 +737,18 @@
     <t>Annual Panic Button Monitoring: S</t>
   </si>
   <si>
+    <t>SOUTHLAND INDUSTRIES</t>
+  </si>
+  <si>
+    <t>5 hours Labor - HVAC Repair AAON</t>
+  </si>
+  <si>
+    <t>(4) Crank Case Heaters</t>
+  </si>
+  <si>
+    <t>Service Vehicle Fee</t>
+  </si>
+  <si>
     <t>100-40-450-5374-</t>
   </si>
   <si>
@@ -810,12 +834,6 @@
   </si>
   <si>
     <t>Monthly billboard placement for 3</t>
-  </si>
-  <si>
-    <t>Billboard Production</t>
-  </si>
-  <si>
-    <t>Billboard Installation</t>
   </si>
   <si>
     <t>100-70-710-5116-</t>
@@ -1452,8 +1470,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2a7e3f1e-3de9-48fc-9aa1-cbf66648163e}">
-  <dimension ref="A1:Q157"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{872fe8e1-9d70-4c93-aebf-c24cfe41d0fe}">
+  <dimension ref="A1:Q161"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="15.5714285714286" style="3" customWidth="1"/>
@@ -1575,7 +1593,7 @@
         <v>100000</v>
       </c>
       <c r="P2" s="9">
-        <v>36743.74</v>
+        <v>36281.74</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>27</v>
@@ -3300,7 +3318,7 @@
         <v>23</v>
       </c>
       <c r="H35" s="5">
-        <v>2620071</v>
+        <v>2620155</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>24</v>
@@ -3312,22 +3330,22 @@
         <v>1</v>
       </c>
       <c r="L35" s="5">
-        <v>1428</v>
+        <v>1056</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="N35" s="7">
-        <v>45937</v>
+        <v>45951</v>
       </c>
       <c r="O35" s="9">
-        <v>5000</v>
+        <v>65000</v>
       </c>
       <c r="P35" s="9">
-        <v>5000</v>
+        <v>3432.94</v>
       </c>
       <c r="Q35" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="12.75">
@@ -3353,7 +3371,7 @@
         <v>23</v>
       </c>
       <c r="H36" s="5">
-        <v>2620155</v>
+        <v>2620418</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>24</v>
@@ -3365,22 +3383,22 @@
         <v>1</v>
       </c>
       <c r="L36" s="5">
-        <v>1056</v>
+        <v>1158</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N36" s="7">
-        <v>45951</v>
+        <v>46142</v>
       </c>
       <c r="O36" s="9">
-        <v>65000</v>
+        <v>6862.80</v>
       </c>
       <c r="P36" s="9">
-        <v>3432.94</v>
+        <v>6862.80</v>
       </c>
       <c r="Q36" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" spans="1:17" ht="12.75">
@@ -3415,22 +3433,22 @@
         <v>25</v>
       </c>
       <c r="K37" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L37" s="5">
         <v>1158</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N37" s="7">
         <v>46142</v>
       </c>
       <c r="O37" s="9">
-        <v>6862.80</v>
+        <v>385.20</v>
       </c>
       <c r="P37" s="9">
-        <v>6862.80</v>
+        <v>385.20</v>
       </c>
       <c r="Q37" s="3" t="s">
         <v>94</v>
@@ -3468,22 +3486,22 @@
         <v>25</v>
       </c>
       <c r="K38" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L38" s="5">
         <v>1158</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N38" s="7">
         <v>46142</v>
       </c>
       <c r="O38" s="9">
-        <v>385.20</v>
+        <v>125</v>
       </c>
       <c r="P38" s="9">
-        <v>385.20</v>
+        <v>96.50</v>
       </c>
       <c r="Q38" s="3" t="s">
         <v>95</v>
@@ -3512,7 +3530,7 @@
         <v>23</v>
       </c>
       <c r="H39" s="5">
-        <v>2620418</v>
+        <v>2620482</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>24</v>
@@ -3521,25 +3539,25 @@
         <v>25</v>
       </c>
       <c r="K39" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L39" s="5">
-        <v>1158</v>
+        <v>5194</v>
       </c>
       <c r="M39" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="N39" s="7">
-        <v>46142</v>
+        <v>46210</v>
       </c>
       <c r="O39" s="9">
-        <v>125</v>
+        <v>74.95</v>
       </c>
       <c r="P39" s="9">
-        <v>96.50</v>
+        <v>74.95</v>
       </c>
       <c r="Q39" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="12.75">
@@ -3574,22 +3592,22 @@
         <v>25</v>
       </c>
       <c r="K40" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L40" s="5">
         <v>5194</v>
       </c>
       <c r="M40" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N40" s="7">
         <v>46210</v>
       </c>
       <c r="O40" s="9">
-        <v>74.95</v>
+        <v>29.95</v>
       </c>
       <c r="P40" s="9">
-        <v>74.95</v>
+        <v>29.95</v>
       </c>
       <c r="Q40" s="3" t="s">
         <v>98</v>
@@ -3627,22 +3645,22 @@
         <v>25</v>
       </c>
       <c r="K41" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L41" s="5">
         <v>5194</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N41" s="7">
         <v>46210</v>
       </c>
       <c r="O41" s="9">
-        <v>29.95</v>
+        <v>24.95</v>
       </c>
       <c r="P41" s="9">
-        <v>29.95</v>
+        <v>24.95</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>99</v>
@@ -3680,13 +3698,13 @@
         <v>25</v>
       </c>
       <c r="K42" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L42" s="5">
         <v>5194</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N42" s="7">
         <v>46210</v>
@@ -3733,22 +3751,22 @@
         <v>25</v>
       </c>
       <c r="K43" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L43" s="5">
         <v>5194</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N43" s="7">
         <v>46210</v>
       </c>
       <c r="O43" s="9">
-        <v>24.95</v>
+        <v>67.76</v>
       </c>
       <c r="P43" s="9">
-        <v>24.95</v>
+        <v>67.76</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>101</v>
@@ -3786,22 +3804,22 @@
         <v>25</v>
       </c>
       <c r="K44" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L44" s="5">
         <v>5194</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N44" s="7">
         <v>46210</v>
       </c>
       <c r="O44" s="9">
-        <v>67.76</v>
+        <v>99.95</v>
       </c>
       <c r="P44" s="9">
-        <v>67.76</v>
+        <v>99.95</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>102</v>
@@ -3839,13 +3857,13 @@
         <v>25</v>
       </c>
       <c r="K45" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L45" s="5">
         <v>5194</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N45" s="7">
         <v>46210</v>
@@ -3892,13 +3910,13 @@
         <v>25</v>
       </c>
       <c r="K46" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L46" s="5">
         <v>5194</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N46" s="7">
         <v>46210</v>
@@ -3945,13 +3963,13 @@
         <v>25</v>
       </c>
       <c r="K47" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L47" s="5">
         <v>5194</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N47" s="7">
         <v>46210</v>
@@ -3998,13 +4016,13 @@
         <v>25</v>
       </c>
       <c r="K48" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L48" s="5">
         <v>5194</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N48" s="7">
         <v>46210</v>
@@ -4051,13 +4069,13 @@
         <v>25</v>
       </c>
       <c r="K49" s="5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L49" s="5">
         <v>5194</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N49" s="7">
         <v>46210</v>
@@ -4104,22 +4122,22 @@
         <v>25</v>
       </c>
       <c r="K50" s="5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L50" s="5">
         <v>5194</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N50" s="7">
         <v>46210</v>
       </c>
       <c r="O50" s="9">
-        <v>99.95</v>
+        <v>11.95</v>
       </c>
       <c r="P50" s="9">
-        <v>99.95</v>
+        <v>11.95</v>
       </c>
       <c r="Q50" s="3" t="s">
         <v>108</v>
@@ -4157,22 +4175,22 @@
         <v>25</v>
       </c>
       <c r="K51" s="5">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L51" s="5">
         <v>5194</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N51" s="7">
         <v>46210</v>
       </c>
       <c r="O51" s="9">
-        <v>11.95</v>
+        <v>511.30</v>
       </c>
       <c r="P51" s="9">
-        <v>11.95</v>
+        <v>511.30</v>
       </c>
       <c r="Q51" s="3" t="s">
         <v>109</v>
@@ -4210,22 +4228,22 @@
         <v>25</v>
       </c>
       <c r="K52" s="5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L52" s="5">
         <v>5194</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N52" s="7">
         <v>46210</v>
       </c>
       <c r="O52" s="9">
-        <v>511.30</v>
+        <v>74.71</v>
       </c>
       <c r="P52" s="9">
-        <v>511.30</v>
+        <v>74.71</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>110</v>
@@ -4263,22 +4281,22 @@
         <v>25</v>
       </c>
       <c r="K53" s="5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L53" s="5">
         <v>5194</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N53" s="7">
         <v>46210</v>
       </c>
       <c r="O53" s="9">
-        <v>74.71</v>
+        <v>114.95</v>
       </c>
       <c r="P53" s="9">
-        <v>74.71</v>
+        <v>114.95</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>111</v>
@@ -4316,13 +4334,13 @@
         <v>25</v>
       </c>
       <c r="K54" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L54" s="5">
         <v>5194</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N54" s="7">
         <v>46210</v>
@@ -4334,7 +4352,7 @@
         <v>114.95</v>
       </c>
       <c r="Q54" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="55" spans="1:17" ht="12.75">
@@ -4369,13 +4387,13 @@
         <v>25</v>
       </c>
       <c r="K55" s="5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L55" s="5">
         <v>5194</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N55" s="7">
         <v>46210</v>
@@ -4387,7 +4405,7 @@
         <v>114.95</v>
       </c>
       <c r="Q55" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="56" spans="1:17" ht="12.75">
@@ -4422,22 +4440,22 @@
         <v>25</v>
       </c>
       <c r="K56" s="5">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L56" s="5">
         <v>5194</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N56" s="7">
         <v>46210</v>
       </c>
       <c r="O56" s="9">
-        <v>114.95</v>
+        <v>342.95</v>
       </c>
       <c r="P56" s="9">
-        <v>114.95</v>
+        <v>342.95</v>
       </c>
       <c r="Q56" s="3" t="s">
         <v>112</v>
@@ -4475,22 +4493,22 @@
         <v>25</v>
       </c>
       <c r="K57" s="5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L57" s="5">
         <v>5194</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N57" s="7">
         <v>46210</v>
       </c>
       <c r="O57" s="9">
-        <v>342.95</v>
+        <v>24.95</v>
       </c>
       <c r="P57" s="9">
-        <v>342.95</v>
+        <v>24.95</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>113</v>
@@ -4528,22 +4546,22 @@
         <v>25</v>
       </c>
       <c r="K58" s="5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L58" s="5">
         <v>5194</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N58" s="7">
         <v>46210</v>
       </c>
       <c r="O58" s="9">
-        <v>24.95</v>
+        <v>99.95</v>
       </c>
       <c r="P58" s="9">
-        <v>24.95</v>
+        <v>99.95</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>114</v>
@@ -4581,22 +4599,22 @@
         <v>25</v>
       </c>
       <c r="K59" s="5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L59" s="5">
         <v>5194</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N59" s="7">
         <v>46210</v>
       </c>
       <c r="O59" s="9">
-        <v>99.95</v>
+        <v>74.95</v>
       </c>
       <c r="P59" s="9">
-        <v>99.95</v>
+        <v>74.95</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>115</v>
@@ -4634,22 +4652,22 @@
         <v>25</v>
       </c>
       <c r="K60" s="5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L60" s="5">
         <v>5194</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N60" s="7">
         <v>46210</v>
       </c>
       <c r="O60" s="9">
-        <v>74.95</v>
+        <v>29.95</v>
       </c>
       <c r="P60" s="9">
-        <v>74.95</v>
+        <v>29.95</v>
       </c>
       <c r="Q60" s="3" t="s">
         <v>116</v>
@@ -4687,22 +4705,22 @@
         <v>25</v>
       </c>
       <c r="K61" s="5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L61" s="5">
         <v>5194</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N61" s="7">
         <v>46210</v>
       </c>
       <c r="O61" s="9">
-        <v>29.95</v>
+        <v>24.95</v>
       </c>
       <c r="P61" s="9">
-        <v>29.95</v>
+        <v>24.95</v>
       </c>
       <c r="Q61" s="3" t="s">
         <v>117</v>
@@ -4740,25 +4758,25 @@
         <v>25</v>
       </c>
       <c r="K62" s="5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L62" s="5">
         <v>5194</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N62" s="7">
         <v>46210</v>
       </c>
       <c r="O62" s="9">
-        <v>24.95</v>
+        <v>134.95</v>
       </c>
       <c r="P62" s="9">
-        <v>24.95</v>
+        <v>134.95</v>
       </c>
       <c r="Q62" s="3" t="s">
-        <v>118</v>
+        <v>49</v>
       </c>
     </row>
     <row r="63" spans="1:17" ht="12.75">
@@ -4793,25 +4811,25 @@
         <v>25</v>
       </c>
       <c r="K63" s="5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L63" s="5">
         <v>5194</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N63" s="7">
         <v>46210</v>
       </c>
       <c r="O63" s="9">
-        <v>134.95</v>
+        <v>28.60</v>
       </c>
       <c r="P63" s="9">
-        <v>134.95</v>
+        <v>28.60</v>
       </c>
       <c r="Q63" s="3" t="s">
-        <v>49</v>
+        <v>118</v>
       </c>
     </row>
     <row r="64" spans="1:17" ht="12.75">
@@ -4846,22 +4864,22 @@
         <v>25</v>
       </c>
       <c r="K64" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L64" s="5">
         <v>5194</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N64" s="7">
         <v>46210</v>
       </c>
       <c r="O64" s="9">
-        <v>28.60</v>
+        <v>90</v>
       </c>
       <c r="P64" s="9">
-        <v>28.60</v>
+        <v>90</v>
       </c>
       <c r="Q64" s="3" t="s">
         <v>119</v>
@@ -4890,7 +4908,7 @@
         <v>23</v>
       </c>
       <c r="H65" s="5">
-        <v>2620482</v>
+        <v>2620490</v>
       </c>
       <c r="I65" s="3" t="s">
         <v>24</v>
@@ -4899,22 +4917,22 @@
         <v>25</v>
       </c>
       <c r="K65" s="5">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="L65" s="5">
-        <v>5194</v>
+        <v>1158</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="N65" s="7">
-        <v>46210</v>
+        <v>46223</v>
       </c>
       <c r="O65" s="9">
-        <v>90</v>
+        <v>1143.80</v>
       </c>
       <c r="P65" s="9">
-        <v>90</v>
+        <v>1143.80</v>
       </c>
       <c r="Q65" s="3" t="s">
         <v>120</v>
@@ -4952,13 +4970,13 @@
         <v>25</v>
       </c>
       <c r="K66" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L66" s="5">
         <v>1158</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N66" s="7">
         <v>46223</v>
@@ -5005,13 +5023,13 @@
         <v>25</v>
       </c>
       <c r="K67" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L67" s="5">
         <v>1158</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N67" s="7">
         <v>46223</v>
@@ -5023,7 +5041,7 @@
         <v>1143.80</v>
       </c>
       <c r="Q67" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="68" spans="1:17" ht="12.75">
@@ -5058,13 +5076,13 @@
         <v>25</v>
       </c>
       <c r="K68" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L68" s="5">
         <v>1158</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N68" s="7">
         <v>46223</v>
@@ -5111,13 +5129,13 @@
         <v>25</v>
       </c>
       <c r="K69" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L69" s="5">
         <v>1158</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N69" s="7">
         <v>46223</v>
@@ -5164,13 +5182,13 @@
         <v>25</v>
       </c>
       <c r="K70" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L70" s="5">
         <v>1158</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N70" s="7">
         <v>46223</v>
@@ -5182,7 +5200,7 @@
         <v>1143.80</v>
       </c>
       <c r="Q70" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="71" spans="1:17" ht="12.75">
@@ -5217,25 +5235,25 @@
         <v>25</v>
       </c>
       <c r="K71" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L71" s="5">
         <v>1158</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N71" s="7">
         <v>46223</v>
       </c>
       <c r="O71" s="9">
-        <v>1143.80</v>
+        <v>385.20</v>
       </c>
       <c r="P71" s="9">
-        <v>1143.80</v>
+        <v>385.20</v>
       </c>
       <c r="Q71" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="72" spans="1:17" ht="12.75">
@@ -5270,22 +5288,22 @@
         <v>25</v>
       </c>
       <c r="K72" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L72" s="5">
         <v>1158</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N72" s="7">
         <v>46223</v>
       </c>
       <c r="O72" s="9">
-        <v>385.20</v>
+        <v>345.35</v>
       </c>
       <c r="P72" s="9">
-        <v>385.20</v>
+        <v>345.35</v>
       </c>
       <c r="Q72" s="3" t="s">
         <v>125</v>
@@ -5323,22 +5341,22 @@
         <v>25</v>
       </c>
       <c r="K73" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L73" s="5">
         <v>1158</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="N73" s="7">
         <v>46223</v>
       </c>
       <c r="O73" s="9">
-        <v>345.35</v>
+        <v>125</v>
       </c>
       <c r="P73" s="9">
-        <v>345.35</v>
+        <v>125</v>
       </c>
       <c r="Q73" s="3" t="s">
         <v>126</v>
@@ -5367,7 +5385,7 @@
         <v>23</v>
       </c>
       <c r="H74" s="5">
-        <v>2620490</v>
+        <v>2620498</v>
       </c>
       <c r="I74" s="3" t="s">
         <v>24</v>
@@ -5376,39 +5394,39 @@
         <v>25</v>
       </c>
       <c r="K74" s="5">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L74" s="5">
-        <v>1158</v>
+        <v>5057</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>93</v>
+        <v>127</v>
       </c>
       <c r="N74" s="7">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O74" s="9">
-        <v>125</v>
+        <v>142.50</v>
       </c>
       <c r="P74" s="9">
-        <v>125</v>
+        <v>142.50</v>
       </c>
       <c r="Q74" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="75" spans="1:17" ht="12.75">
       <c r="A75" s="3" t="s">
-        <v>128</v>
+        <v>88</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>129</v>
+        <v>19</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>21</v>
@@ -5420,7 +5438,7 @@
         <v>23</v>
       </c>
       <c r="H75" s="5">
-        <v>2620457</v>
+        <v>2620498</v>
       </c>
       <c r="I75" s="3" t="s">
         <v>24</v>
@@ -5429,39 +5447,39 @@
         <v>25</v>
       </c>
       <c r="K75" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L75" s="5">
-        <v>5187</v>
+        <v>5057</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>64</v>
+        <v>127</v>
       </c>
       <c r="N75" s="7">
-        <v>46184</v>
+        <v>46224</v>
       </c>
       <c r="O75" s="9">
-        <v>2827</v>
+        <v>1567.50</v>
       </c>
       <c r="P75" s="9">
-        <v>2827</v>
+        <v>1567.50</v>
       </c>
       <c r="Q75" s="3" t="s">
-        <v>65</v>
+        <v>129</v>
       </c>
     </row>
     <row r="76" spans="1:17" ht="12.75">
       <c r="A76" s="3" t="s">
-        <v>128</v>
+        <v>88</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>129</v>
+        <v>19</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>21</v>
@@ -5473,7 +5491,7 @@
         <v>23</v>
       </c>
       <c r="H76" s="5">
-        <v>2620457</v>
+        <v>2620498</v>
       </c>
       <c r="I76" s="3" t="s">
         <v>24</v>
@@ -5482,39 +5500,39 @@
         <v>25</v>
       </c>
       <c r="K76" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L76" s="5">
-        <v>5187</v>
+        <v>5057</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>64</v>
+        <v>127</v>
       </c>
       <c r="N76" s="7">
-        <v>46184</v>
+        <v>46224</v>
       </c>
       <c r="O76" s="9">
-        <v>56.25</v>
+        <v>3847.50</v>
       </c>
       <c r="P76" s="9">
-        <v>56.25</v>
+        <v>3847.50</v>
       </c>
       <c r="Q76" s="3" t="s">
-        <v>66</v>
+        <v>130</v>
       </c>
     </row>
     <row r="77" spans="1:17" ht="12.75">
       <c r="A77" s="3" t="s">
-        <v>130</v>
+        <v>88</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>129</v>
+        <v>19</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>21</v>
@@ -5526,7 +5544,7 @@
         <v>23</v>
       </c>
       <c r="H77" s="5">
-        <v>2620072</v>
+        <v>2620498</v>
       </c>
       <c r="I77" s="3" t="s">
         <v>24</v>
@@ -5535,39 +5553,39 @@
         <v>25</v>
       </c>
       <c r="K77" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L77" s="5">
-        <v>1020</v>
+        <v>5057</v>
       </c>
       <c r="M77" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="N77" s="7">
+        <v>46224</v>
+      </c>
+      <c r="O77" s="9">
+        <v>855</v>
+      </c>
+      <c r="P77" s="9">
+        <v>855</v>
+      </c>
+      <c r="Q77" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="N77" s="7">
-        <v>45937</v>
-      </c>
-      <c r="O77" s="9">
-        <v>68708.51</v>
-      </c>
-      <c r="P77" s="9">
-        <v>21678.57</v>
-      </c>
-      <c r="Q77" s="3" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="78" spans="1:17" ht="12.75">
       <c r="A78" s="3" t="s">
-        <v>133</v>
+        <v>88</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>21</v>
@@ -5579,48 +5597,48 @@
         <v>23</v>
       </c>
       <c r="H78" s="5">
-        <v>2620149</v>
+        <v>2620498</v>
       </c>
       <c r="I78" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J78" s="3" t="s">
-        <v>137</v>
+        <v>25</v>
       </c>
       <c r="K78" s="5">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L78" s="5">
-        <v>1252</v>
+        <v>5057</v>
       </c>
       <c r="M78" s="3" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="N78" s="7">
-        <v>45947</v>
+        <v>46224</v>
       </c>
       <c r="O78" s="9">
-        <v>54000</v>
+        <v>122.16</v>
       </c>
       <c r="P78" s="9">
-        <v>22772.48</v>
+        <v>122.16</v>
       </c>
       <c r="Q78" s="3" t="s">
-        <v>139</v>
+        <v>95</v>
       </c>
     </row>
     <row r="79" spans="1:17" ht="12.75">
       <c r="A79" s="3" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>21</v>
@@ -5632,48 +5650,48 @@
         <v>23</v>
       </c>
       <c r="H79" s="5">
-        <v>2620151</v>
+        <v>2620457</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>137</v>
+        <v>25</v>
       </c>
       <c r="K79" s="5">
         <v>1</v>
       </c>
       <c r="L79" s="5">
-        <v>4034</v>
+        <v>5187</v>
       </c>
       <c r="M79" s="3" t="s">
-        <v>141</v>
+        <v>64</v>
       </c>
       <c r="N79" s="7">
-        <v>45947</v>
+        <v>46184</v>
       </c>
       <c r="O79" s="9">
-        <v>40000</v>
+        <v>2827</v>
       </c>
       <c r="P79" s="9">
-        <v>6666.70</v>
+        <v>2827</v>
       </c>
       <c r="Q79" s="3" t="s">
-        <v>142</v>
+        <v>65</v>
       </c>
     </row>
     <row r="80" spans="1:17" ht="12.75">
       <c r="A80" s="3" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>21</v>
@@ -5685,154 +5703,154 @@
         <v>23</v>
       </c>
       <c r="H80" s="5">
-        <v>2620135</v>
+        <v>2620457</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J80" s="3" t="s">
-        <v>145</v>
+        <v>25</v>
       </c>
       <c r="K80" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L80" s="5">
-        <v>1238</v>
+        <v>5187</v>
       </c>
       <c r="M80" s="3" t="s">
-        <v>146</v>
+        <v>64</v>
       </c>
       <c r="N80" s="7">
-        <v>45947</v>
+        <v>46184</v>
       </c>
       <c r="O80" s="9">
-        <v>54000</v>
+        <v>56.25</v>
       </c>
       <c r="P80" s="9">
-        <v>23520</v>
+        <v>56.25</v>
       </c>
       <c r="Q80" s="3" t="s">
-        <v>147</v>
+        <v>66</v>
       </c>
     </row>
     <row r="81" spans="1:17" ht="12.75">
       <c r="A81" s="3" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>149</v>
+        <v>68</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>151</v>
+        <v>69</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>152</v>
+        <v>22</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>153</v>
+        <v>23</v>
       </c>
       <c r="H81" s="5">
-        <v>2620342</v>
+        <v>2620072</v>
       </c>
       <c r="I81" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>154</v>
+        <v>25</v>
       </c>
       <c r="K81" s="5">
         <v>1</v>
       </c>
       <c r="L81" s="5">
-        <v>1987</v>
+        <v>1020</v>
       </c>
       <c r="M81" s="3" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="N81" s="7">
-        <v>46069</v>
+        <v>45937</v>
       </c>
       <c r="O81" s="9">
-        <v>3161.92</v>
+        <v>68708.51</v>
       </c>
       <c r="P81" s="9">
-        <v>3161.92</v>
+        <v>21678.57</v>
       </c>
       <c r="Q81" s="3" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
     </row>
     <row r="82" spans="1:17" ht="12.75">
       <c r="A82" s="3" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="E82" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>152</v>
+        <v>22</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>153</v>
+        <v>23</v>
       </c>
       <c r="H82" s="5">
-        <v>2620389</v>
+        <v>2620149</v>
       </c>
       <c r="I82" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J82" s="3" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="K82" s="5">
         <v>1</v>
       </c>
       <c r="L82" s="5">
-        <v>1402</v>
+        <v>1252</v>
       </c>
       <c r="M82" s="3" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="N82" s="7">
-        <v>46111</v>
+        <v>45947</v>
       </c>
       <c r="O82" s="9">
-        <v>555.80</v>
+        <v>54000</v>
       </c>
       <c r="P82" s="9">
-        <v>555.80</v>
+        <v>22772.48</v>
       </c>
       <c r="Q82" s="3" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
     </row>
     <row r="83" spans="1:17" ht="12.75">
       <c r="A83" s="3" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>149</v>
+        <v>68</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>151</v>
+        <v>69</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>21</v>
@@ -5844,48 +5862,48 @@
         <v>23</v>
       </c>
       <c r="H83" s="5">
-        <v>2620370</v>
+        <v>2620151</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="K83" s="5">
         <v>1</v>
       </c>
       <c r="L83" s="5">
-        <v>2214</v>
+        <v>4034</v>
       </c>
       <c r="M83" s="3" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="N83" s="7">
-        <v>46097</v>
+        <v>45947</v>
       </c>
       <c r="O83" s="9">
-        <v>10560</v>
+        <v>40000</v>
       </c>
       <c r="P83" s="9">
-        <v>2795.04</v>
+        <v>6666.70</v>
       </c>
       <c r="Q83" s="3" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
     </row>
     <row r="84" spans="1:17" ht="12.75">
       <c r="A84" s="3" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>165</v>
+        <v>68</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="E84" s="3" t="s">
         <v>21</v>
@@ -5897,207 +5915,207 @@
         <v>23</v>
       </c>
       <c r="H84" s="5">
-        <v>2620162</v>
+        <v>2620135</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J84" s="3" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="K84" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L84" s="5">
-        <v>1868</v>
+        <v>1238</v>
       </c>
       <c r="M84" s="3" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="N84" s="7">
-        <v>45953</v>
+        <v>45947</v>
       </c>
       <c r="O84" s="9">
-        <v>33935.65</v>
+        <v>54000</v>
       </c>
       <c r="P84" s="9">
-        <v>19071.76</v>
+        <v>23520</v>
       </c>
       <c r="Q84" s="3" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
     </row>
     <row r="85" spans="1:17" ht="12.75">
       <c r="A85" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>22</v>
+        <v>156</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>23</v>
+        <v>157</v>
       </c>
       <c r="H85" s="5">
-        <v>2620162</v>
+        <v>2620342</v>
       </c>
       <c r="I85" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="K85" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L85" s="5">
-        <v>1868</v>
+        <v>1987</v>
       </c>
       <c r="M85" s="3" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="N85" s="7">
-        <v>45953</v>
+        <v>46069</v>
       </c>
       <c r="O85" s="9">
-        <v>18453.49</v>
+        <v>3161.92</v>
       </c>
       <c r="P85" s="9">
-        <v>18453.49</v>
+        <v>3161.92</v>
       </c>
       <c r="Q85" s="3" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
     </row>
     <row r="86" spans="1:17" ht="12.75">
       <c r="A86" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>22</v>
+        <v>156</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>23</v>
+        <v>157</v>
       </c>
       <c r="H86" s="5">
-        <v>2620162</v>
+        <v>2620389</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J86" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="K86" s="5">
+        <v>1</v>
+      </c>
+      <c r="L86" s="5">
+        <v>1402</v>
+      </c>
+      <c r="M86" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="K86" s="5">
-        <v>4</v>
-      </c>
-      <c r="L86" s="5">
-        <v>1868</v>
-      </c>
-      <c r="M86" s="3" t="s">
-        <v>168</v>
-      </c>
       <c r="N86" s="7">
-        <v>45953</v>
+        <v>46111</v>
       </c>
       <c r="O86" s="9">
-        <v>10116.86</v>
+        <v>555.80</v>
       </c>
       <c r="P86" s="9">
-        <v>8397.66</v>
+        <v>555.80</v>
       </c>
       <c r="Q86" s="3" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
     </row>
     <row r="87" spans="1:17" ht="12.75">
       <c r="A87" s="3" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="C87" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H87" s="5">
+        <v>2620370</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J87" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="K87" s="5">
+        <v>1</v>
+      </c>
+      <c r="L87" s="5">
+        <v>2214</v>
+      </c>
+      <c r="M87" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="D87" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G87" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H87" s="5">
-        <v>2620162</v>
-      </c>
-      <c r="I87" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J87" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="K87" s="5">
-        <v>5</v>
-      </c>
-      <c r="L87" s="5">
-        <v>1868</v>
-      </c>
-      <c r="M87" s="3" t="s">
-        <v>168</v>
-      </c>
       <c r="N87" s="7">
-        <v>45953</v>
+        <v>46097</v>
       </c>
       <c r="O87" s="9">
-        <v>8568.70</v>
+        <v>10560</v>
       </c>
       <c r="P87" s="9">
-        <v>5430</v>
+        <v>2795.04</v>
       </c>
       <c r="Q87" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="88" spans="1:17" ht="12.75">
       <c r="A88" s="3" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>68</v>
+        <v>169</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>69</v>
+        <v>171</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>21</v>
@@ -6109,48 +6127,48 @@
         <v>23</v>
       </c>
       <c r="H88" s="5">
-        <v>2620040</v>
+        <v>2620162</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J88" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K88" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L88" s="5">
-        <v>3836</v>
+        <v>1868</v>
       </c>
       <c r="M88" s="3" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="N88" s="7">
-        <v>45931</v>
+        <v>45953</v>
       </c>
       <c r="O88" s="9">
-        <v>83500</v>
+        <v>33935.65</v>
       </c>
       <c r="P88" s="9">
-        <v>6958.37</v>
+        <v>19071.76</v>
       </c>
       <c r="Q88" s="3" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="89" spans="1:17" ht="12.75">
       <c r="A89" s="3" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>68</v>
+        <v>169</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>69</v>
+        <v>171</v>
       </c>
       <c r="E89" s="3" t="s">
         <v>21</v>
@@ -6162,48 +6180,48 @@
         <v>23</v>
       </c>
       <c r="H89" s="5">
-        <v>2620407</v>
+        <v>2620162</v>
       </c>
       <c r="I89" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J89" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K89" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L89" s="5">
-        <v>1632</v>
+        <v>1868</v>
       </c>
       <c r="M89" s="3" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="N89" s="7">
-        <v>46129</v>
+        <v>45953</v>
       </c>
       <c r="O89" s="9">
-        <v>1620</v>
+        <v>18453.49</v>
       </c>
       <c r="P89" s="9">
-        <v>1620</v>
+        <v>18453.49</v>
       </c>
       <c r="Q89" s="3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
     </row>
     <row r="90" spans="1:17" ht="12.75">
       <c r="A90" s="3" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>68</v>
+        <v>169</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>69</v>
+        <v>171</v>
       </c>
       <c r="E90" s="3" t="s">
         <v>21</v>
@@ -6215,34 +6233,34 @@
         <v>23</v>
       </c>
       <c r="H90" s="5">
-        <v>2620407</v>
+        <v>2620162</v>
       </c>
       <c r="I90" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K90" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L90" s="5">
-        <v>1632</v>
+        <v>1868</v>
       </c>
       <c r="M90" s="3" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="N90" s="7">
-        <v>46129</v>
+        <v>45953</v>
       </c>
       <c r="O90" s="9">
-        <v>400</v>
+        <v>10116.86</v>
       </c>
       <c r="P90" s="9">
-        <v>400</v>
+        <v>8397.66</v>
       </c>
       <c r="Q90" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="91" spans="1:17" ht="12.75">
@@ -6250,13 +6268,13 @@
         <v>176</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>68</v>
+        <v>177</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>69</v>
+        <v>178</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>21</v>
@@ -6268,45 +6286,45 @@
         <v>23</v>
       </c>
       <c r="H91" s="5">
-        <v>2620407</v>
+        <v>2620162</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K91" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L91" s="5">
-        <v>1632</v>
+        <v>1868</v>
       </c>
       <c r="M91" s="3" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="N91" s="7">
-        <v>46129</v>
+        <v>45953</v>
       </c>
       <c r="O91" s="9">
-        <v>2042.50</v>
+        <v>8568.70</v>
       </c>
       <c r="P91" s="9">
-        <v>2042.50</v>
+        <v>5430</v>
       </c>
       <c r="Q91" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="92" spans="1:17" ht="12.75">
       <c r="A92" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>69</v>
@@ -6321,45 +6339,45 @@
         <v>23</v>
       </c>
       <c r="H92" s="5">
-        <v>2620407</v>
+        <v>2620040</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K92" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L92" s="5">
-        <v>1632</v>
+        <v>3836</v>
       </c>
       <c r="M92" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="N92" s="7">
-        <v>46129</v>
+        <v>45931</v>
       </c>
       <c r="O92" s="9">
-        <v>150</v>
+        <v>83500</v>
       </c>
       <c r="P92" s="9">
-        <v>150</v>
+        <v>6958.37</v>
       </c>
       <c r="Q92" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="93" spans="1:17" ht="12.75">
       <c r="A93" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>69</v>
@@ -6380,39 +6398,39 @@
         <v>24</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K93" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L93" s="5">
         <v>1632</v>
       </c>
       <c r="M93" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="N93" s="7">
         <v>46129</v>
       </c>
       <c r="O93" s="9">
-        <v>600</v>
+        <v>1620</v>
       </c>
       <c r="P93" s="9">
-        <v>600</v>
+        <v>1620</v>
       </c>
       <c r="Q93" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="94" spans="1:17" ht="12.75">
       <c r="A94" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>69</v>
@@ -6433,39 +6451,39 @@
         <v>24</v>
       </c>
       <c r="J94" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K94" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L94" s="5">
         <v>1632</v>
       </c>
       <c r="M94" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="N94" s="7">
         <v>46129</v>
       </c>
       <c r="O94" s="9">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="P94" s="9">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="Q94" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="95" spans="1:17" ht="12.75">
       <c r="A95" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>69</v>
@@ -6480,45 +6498,45 @@
         <v>23</v>
       </c>
       <c r="H95" s="5">
-        <v>2620487</v>
+        <v>2620407</v>
       </c>
       <c r="I95" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K95" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L95" s="5">
-        <v>5212</v>
+        <v>1632</v>
       </c>
       <c r="M95" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="N95" s="7">
-        <v>46219</v>
+        <v>46129</v>
       </c>
       <c r="O95" s="9">
-        <v>295</v>
+        <v>2042.50</v>
       </c>
       <c r="P95" s="9">
-        <v>295</v>
+        <v>2042.50</v>
       </c>
       <c r="Q95" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="96" spans="1:17" ht="12.75">
       <c r="A96" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>69</v>
@@ -6533,45 +6551,45 @@
         <v>23</v>
       </c>
       <c r="H96" s="5">
-        <v>2620487</v>
+        <v>2620407</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J96" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K96" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L96" s="5">
-        <v>5212</v>
+        <v>1632</v>
       </c>
       <c r="M96" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="N96" s="7">
-        <v>46219</v>
+        <v>46129</v>
       </c>
       <c r="O96" s="9">
-        <v>295</v>
+        <v>150</v>
       </c>
       <c r="P96" s="9">
-        <v>295</v>
+        <v>150</v>
       </c>
       <c r="Q96" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="97" spans="1:17" ht="12.75">
       <c r="A97" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>69</v>
@@ -6586,45 +6604,45 @@
         <v>23</v>
       </c>
       <c r="H97" s="5">
-        <v>2620487</v>
+        <v>2620407</v>
       </c>
       <c r="I97" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J97" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K97" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L97" s="5">
-        <v>5212</v>
+        <v>1632</v>
       </c>
       <c r="M97" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="N97" s="7">
-        <v>46219</v>
+        <v>46129</v>
       </c>
       <c r="O97" s="9">
-        <v>295</v>
+        <v>600</v>
       </c>
       <c r="P97" s="9">
-        <v>295</v>
+        <v>600</v>
       </c>
       <c r="Q97" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="98" spans="1:17" ht="12.75">
       <c r="A98" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>69</v>
@@ -6639,45 +6657,45 @@
         <v>23</v>
       </c>
       <c r="H98" s="5">
-        <v>2620487</v>
+        <v>2620407</v>
       </c>
       <c r="I98" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K98" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L98" s="5">
-        <v>5212</v>
+        <v>1632</v>
       </c>
       <c r="M98" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="N98" s="7">
-        <v>46219</v>
+        <v>46129</v>
       </c>
       <c r="O98" s="9">
-        <v>295</v>
+        <v>600</v>
       </c>
       <c r="P98" s="9">
-        <v>295</v>
+        <v>600</v>
       </c>
       <c r="Q98" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="99" spans="1:17" ht="12.75">
       <c r="A99" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>69</v>
@@ -6698,39 +6716,39 @@
         <v>24</v>
       </c>
       <c r="J99" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K99" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L99" s="5">
         <v>5212</v>
       </c>
       <c r="M99" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="N99" s="7">
         <v>46219</v>
       </c>
       <c r="O99" s="9">
-        <v>395</v>
+        <v>295</v>
       </c>
       <c r="P99" s="9">
-        <v>395</v>
+        <v>295</v>
       </c>
       <c r="Q99" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="100" spans="1:17" ht="12.75">
       <c r="A100" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>69</v>
@@ -6751,39 +6769,39 @@
         <v>24</v>
       </c>
       <c r="J100" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K100" s="5">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L100" s="5">
         <v>5212</v>
       </c>
       <c r="M100" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="N100" s="7">
         <v>46219</v>
       </c>
       <c r="O100" s="9">
-        <v>395</v>
+        <v>295</v>
       </c>
       <c r="P100" s="9">
-        <v>395</v>
+        <v>295</v>
       </c>
       <c r="Q100" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="101" spans="1:17" ht="12.75">
       <c r="A101" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>69</v>
@@ -6804,39 +6822,39 @@
         <v>24</v>
       </c>
       <c r="J101" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K101" s="5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L101" s="5">
         <v>5212</v>
       </c>
       <c r="M101" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="N101" s="7">
         <v>46219</v>
       </c>
       <c r="O101" s="9">
-        <v>395</v>
+        <v>295</v>
       </c>
       <c r="P101" s="9">
-        <v>395</v>
+        <v>295</v>
       </c>
       <c r="Q101" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="102" spans="1:17" ht="12.75">
       <c r="A102" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>69</v>
@@ -6857,39 +6875,39 @@
         <v>24</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K102" s="5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L102" s="5">
         <v>5212</v>
       </c>
       <c r="M102" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="N102" s="7">
         <v>46219</v>
       </c>
       <c r="O102" s="9">
-        <v>395</v>
+        <v>295</v>
       </c>
       <c r="P102" s="9">
-        <v>395</v>
+        <v>295</v>
       </c>
       <c r="Q102" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="103" spans="1:17" ht="12.75">
       <c r="A103" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>69</v>
@@ -6910,16 +6928,16 @@
         <v>24</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K103" s="5">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L103" s="5">
         <v>5212</v>
       </c>
       <c r="M103" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="N103" s="7">
         <v>46219</v>
@@ -6931,18 +6949,18 @@
         <v>395</v>
       </c>
       <c r="Q103" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="104" spans="1:17" ht="12.75">
       <c r="A104" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>69</v>
@@ -6963,16 +6981,16 @@
         <v>24</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K104" s="5">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L104" s="5">
         <v>5212</v>
       </c>
       <c r="M104" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="N104" s="7">
         <v>46219</v>
@@ -6984,18 +7002,18 @@
         <v>395</v>
       </c>
       <c r="Q104" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="105" spans="1:17" ht="12.75">
       <c r="A105" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>69</v>
@@ -7016,39 +7034,39 @@
         <v>24</v>
       </c>
       <c r="J105" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K105" s="5">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L105" s="5">
         <v>5212</v>
       </c>
       <c r="M105" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="N105" s="7">
         <v>46219</v>
       </c>
       <c r="O105" s="9">
-        <v>250</v>
+        <v>395</v>
       </c>
       <c r="P105" s="9">
-        <v>250</v>
+        <v>395</v>
       </c>
       <c r="Q105" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="106" spans="1:17" ht="12.75">
       <c r="A106" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>69</v>
@@ -7069,178 +7087,178 @@
         <v>24</v>
       </c>
       <c r="J106" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="K106" s="5">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L106" s="5">
         <v>5212</v>
       </c>
       <c r="M106" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="N106" s="7">
         <v>46219</v>
       </c>
       <c r="O106" s="9">
-        <v>358</v>
+        <v>395</v>
       </c>
       <c r="P106" s="9">
-        <v>358</v>
+        <v>395</v>
       </c>
       <c r="Q106" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="107" spans="1:17" ht="12.75">
       <c r="A107" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>185</v>
+        <v>68</v>
       </c>
       <c r="C107" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H107" s="5">
+        <v>2620487</v>
+      </c>
+      <c r="I107" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J107" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="K107" s="5">
+        <v>9</v>
+      </c>
+      <c r="L107" s="5">
+        <v>5212</v>
+      </c>
+      <c r="M107" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="D107" s="3" t="s">
+      <c r="N107" s="7">
+        <v>46219</v>
+      </c>
+      <c r="O107" s="9">
+        <v>395</v>
+      </c>
+      <c r="P107" s="9">
+        <v>395</v>
+      </c>
+      <c r="Q107" s="3" t="s">
         <v>187</v>
-      </c>
-      <c r="E107" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F107" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="G107" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="H107" s="5">
-        <v>2620263</v>
-      </c>
-      <c r="I107" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J107" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="K107" s="5">
-        <v>1</v>
-      </c>
-      <c r="L107" s="5">
-        <v>1136</v>
-      </c>
-      <c r="M107" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="N107" s="7">
-        <v>46002</v>
-      </c>
-      <c r="O107" s="9">
-        <v>134953.54</v>
-      </c>
-      <c r="P107" s="9">
-        <v>35211.86</v>
-      </c>
-      <c r="Q107" s="3" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="108" spans="1:17" ht="12.75">
       <c r="A108" s="3" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="B108" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H108" s="5">
+        <v>2620487</v>
+      </c>
+      <c r="I108" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J108" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C108" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D108" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="E108" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F108" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G108" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H108" s="5">
-        <v>2620167</v>
-      </c>
-      <c r="I108" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J108" s="3" t="s">
-        <v>193</v>
-      </c>
       <c r="K108" s="5">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L108" s="5">
-        <v>1620</v>
+        <v>5212</v>
       </c>
       <c r="M108" s="3" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="N108" s="7">
-        <v>45954</v>
+        <v>46219</v>
       </c>
       <c r="O108" s="9">
-        <v>23400</v>
+        <v>395</v>
       </c>
       <c r="P108" s="9">
-        <v>8025</v>
+        <v>395</v>
       </c>
       <c r="Q108" s="3" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
     </row>
     <row r="109" spans="1:17" ht="12.75">
       <c r="A109" s="3" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="B109" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H109" s="5">
+        <v>2620487</v>
+      </c>
+      <c r="I109" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J109" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C109" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="E109" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F109" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G109" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H109" s="5">
-        <v>2620167</v>
-      </c>
-      <c r="I109" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J109" s="3" t="s">
-        <v>193</v>
-      </c>
       <c r="K109" s="5">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L109" s="5">
-        <v>1620</v>
+        <v>5212</v>
       </c>
       <c r="M109" s="3" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="N109" s="7">
-        <v>45954</v>
+        <v>46219</v>
       </c>
       <c r="O109" s="9">
         <v>250</v>
@@ -7249,127 +7267,127 @@
         <v>250</v>
       </c>
       <c r="Q109" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
     </row>
     <row r="110" spans="1:17" ht="12.75">
       <c r="A110" s="3" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="B110" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H110" s="5">
+        <v>2620487</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J110" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C110" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D110" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="E110" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F110" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G110" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H110" s="5">
-        <v>2620167</v>
-      </c>
-      <c r="I110" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J110" s="3" t="s">
-        <v>193</v>
-      </c>
       <c r="K110" s="5">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="L110" s="5">
-        <v>1620</v>
+        <v>5212</v>
       </c>
       <c r="M110" s="3" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="N110" s="7">
-        <v>45954</v>
+        <v>46219</v>
       </c>
       <c r="O110" s="9">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="P110" s="9">
-        <v>225</v>
+        <v>358</v>
       </c>
       <c r="Q110" s="3" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
     </row>
     <row r="111" spans="1:17" ht="12.75">
       <c r="A111" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F111" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B111" s="3" t="s">
+      <c r="G111" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="H111" s="5">
+        <v>2620263</v>
+      </c>
+      <c r="I111" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J111" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C111" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F111" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G111" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H111" s="5">
-        <v>2620167</v>
-      </c>
-      <c r="I111" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J111" s="3" t="s">
-        <v>193</v>
-      </c>
       <c r="K111" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L111" s="5">
-        <v>1620</v>
+        <v>1136</v>
       </c>
       <c r="M111" s="3" t="s">
         <v>194</v>
       </c>
       <c r="N111" s="7">
-        <v>45954</v>
+        <v>46002</v>
       </c>
       <c r="O111" s="9">
-        <v>500</v>
+        <v>134953.54</v>
       </c>
       <c r="P111" s="9">
-        <v>500</v>
+        <v>35211.86</v>
       </c>
       <c r="Q111" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="112" spans="1:17" ht="12.75">
       <c r="A112" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>201</v>
+        <v>171</v>
       </c>
       <c r="E112" s="3" t="s">
         <v>21</v>
@@ -7381,13 +7399,13 @@
         <v>23</v>
       </c>
       <c r="H112" s="5">
-        <v>2620392</v>
+        <v>2620167</v>
       </c>
       <c r="I112" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="K112" s="5">
         <v>1</v>
@@ -7396,33 +7414,33 @@
         <v>1620</v>
       </c>
       <c r="M112" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N112" s="7">
-        <v>46111</v>
+        <v>45954</v>
       </c>
       <c r="O112" s="9">
-        <v>8690</v>
+        <v>23400</v>
       </c>
       <c r="P112" s="9">
-        <v>8690</v>
+        <v>8025</v>
       </c>
       <c r="Q112" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="113" spans="1:17" ht="12.75">
       <c r="A113" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>201</v>
+        <v>171</v>
       </c>
       <c r="E113" s="3" t="s">
         <v>21</v>
@@ -7434,13 +7452,13 @@
         <v>23</v>
       </c>
       <c r="H113" s="5">
-        <v>2620392</v>
+        <v>2620167</v>
       </c>
       <c r="I113" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="K113" s="5">
         <v>2</v>
@@ -7449,33 +7467,33 @@
         <v>1620</v>
       </c>
       <c r="M113" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N113" s="7">
-        <v>46111</v>
+        <v>45954</v>
       </c>
       <c r="O113" s="9">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="P113" s="9">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="Q113" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="114" spans="1:17" ht="12.75">
       <c r="A114" s="3" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>68</v>
+        <v>169</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>69</v>
+        <v>171</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>21</v>
@@ -7487,48 +7505,48 @@
         <v>23</v>
       </c>
       <c r="H114" s="5">
-        <v>2620382</v>
+        <v>2620167</v>
       </c>
       <c r="I114" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J114" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="K114" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L114" s="5">
-        <v>2968</v>
+        <v>1620</v>
       </c>
       <c r="M114" s="3" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="N114" s="7">
-        <v>46101</v>
+        <v>45954</v>
       </c>
       <c r="O114" s="9">
-        <v>10000</v>
+        <v>375</v>
       </c>
       <c r="P114" s="9">
-        <v>3952.96</v>
+        <v>225</v>
       </c>
       <c r="Q114" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="115" spans="1:17" ht="12.75">
       <c r="A115" s="3" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>68</v>
+        <v>169</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>69</v>
+        <v>171</v>
       </c>
       <c r="E115" s="3" t="s">
         <v>21</v>
@@ -7540,48 +7558,48 @@
         <v>23</v>
       </c>
       <c r="H115" s="5">
-        <v>2620388</v>
+        <v>2620167</v>
       </c>
       <c r="I115" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J115" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="K115" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L115" s="5">
-        <v>5125</v>
+        <v>1620</v>
       </c>
       <c r="M115" s="3" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="N115" s="7">
-        <v>46107</v>
+        <v>45954</v>
       </c>
       <c r="O115" s="9">
-        <v>5250</v>
+        <v>500</v>
       </c>
       <c r="P115" s="9">
-        <v>1312.50</v>
+        <v>500</v>
       </c>
       <c r="Q115" s="3" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
     </row>
     <row r="116" spans="1:17" ht="12.75">
       <c r="A116" s="3" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>84</v>
+        <v>204</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>85</v>
+        <v>205</v>
       </c>
       <c r="E116" s="3" t="s">
         <v>21</v>
@@ -7593,48 +7611,48 @@
         <v>23</v>
       </c>
       <c r="H116" s="5">
-        <v>2620444</v>
+        <v>2620392</v>
       </c>
       <c r="I116" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J116" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="K116" s="5">
         <v>1</v>
       </c>
       <c r="L116" s="5">
-        <v>4905</v>
+        <v>1620</v>
       </c>
       <c r="M116" s="3" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="N116" s="7">
-        <v>46169</v>
+        <v>46111</v>
       </c>
       <c r="O116" s="9">
-        <v>795</v>
+        <v>8690</v>
       </c>
       <c r="P116" s="9">
-        <v>795</v>
+        <v>8690</v>
       </c>
       <c r="Q116" s="3" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
     </row>
     <row r="117" spans="1:17" ht="12.75">
       <c r="A117" s="3" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>84</v>
+        <v>204</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>85</v>
+        <v>205</v>
       </c>
       <c r="E117" s="3" t="s">
         <v>21</v>
@@ -7646,98 +7664,98 @@
         <v>23</v>
       </c>
       <c r="H117" s="5">
-        <v>2620444</v>
+        <v>2620392</v>
       </c>
       <c r="I117" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J117" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="K117" s="5">
         <v>2</v>
       </c>
       <c r="L117" s="5">
-        <v>4905</v>
+        <v>1620</v>
       </c>
       <c r="M117" s="3" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="N117" s="7">
-        <v>46169</v>
+        <v>46111</v>
       </c>
       <c r="O117" s="9">
-        <v>795</v>
+        <v>400</v>
       </c>
       <c r="P117" s="9">
-        <v>795</v>
+        <v>400</v>
       </c>
       <c r="Q117" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="118" spans="1:17" ht="12.75">
       <c r="A118" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H118" s="5">
+        <v>2620382</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J118" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="K118" s="5">
+        <v>2</v>
+      </c>
+      <c r="L118" s="5">
+        <v>2968</v>
+      </c>
+      <c r="M118" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="B118" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C118" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D118" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F118" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G118" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H118" s="5">
-        <v>2620444</v>
-      </c>
-      <c r="I118" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J118" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="K118" s="5">
-        <v>3</v>
-      </c>
-      <c r="L118" s="5">
-        <v>4905</v>
-      </c>
-      <c r="M118" s="3" t="s">
+      <c r="N118" s="7">
+        <v>46101</v>
+      </c>
+      <c r="O118" s="9">
+        <v>10000</v>
+      </c>
+      <c r="P118" s="9">
+        <v>3952.96</v>
+      </c>
+      <c r="Q118" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="N118" s="7">
-        <v>46169</v>
-      </c>
-      <c r="O118" s="9">
-        <v>795</v>
-      </c>
-      <c r="P118" s="9">
-        <v>795</v>
-      </c>
-      <c r="Q118" s="3" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="119" spans="1:17" ht="12.75">
       <c r="A119" s="3" t="s">
-        <v>211</v>
+        <v>180</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>212</v>
+        <v>181</v>
       </c>
       <c r="D119" s="3" t="s">
         <v>69</v>
@@ -7746,54 +7764,54 @@
         <v>21</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>188</v>
+        <v>22</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>189</v>
+        <v>23</v>
       </c>
       <c r="H119" s="5">
-        <v>2620382</v>
+        <v>2620388</v>
       </c>
       <c r="I119" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J119" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="K119" s="5">
         <v>1</v>
       </c>
       <c r="L119" s="5">
-        <v>2968</v>
+        <v>5125</v>
       </c>
       <c r="M119" s="3" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="N119" s="7">
-        <v>46101</v>
+        <v>46107</v>
       </c>
       <c r="O119" s="9">
-        <v>18000</v>
+        <v>5250</v>
       </c>
       <c r="P119" s="9">
-        <v>10481.58</v>
+        <v>1312.50</v>
       </c>
       <c r="Q119" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="120" spans="1:17" ht="12.75">
       <c r="A120" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>215</v>
+        <v>84</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>216</v>
+        <v>181</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>217</v>
+        <v>85</v>
       </c>
       <c r="E120" s="3" t="s">
         <v>21</v>
@@ -7805,48 +7823,48 @@
         <v>23</v>
       </c>
       <c r="H120" s="5">
-        <v>2620089</v>
+        <v>2620444</v>
       </c>
       <c r="I120" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J120" s="3" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="K120" s="5">
         <v>1</v>
       </c>
       <c r="L120" s="5">
-        <v>1206</v>
+        <v>4905</v>
       </c>
       <c r="M120" s="3" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="N120" s="7">
-        <v>45943</v>
+        <v>46169</v>
       </c>
       <c r="O120" s="9">
-        <v>2755.20</v>
+        <v>795</v>
       </c>
       <c r="P120" s="9">
-        <v>495.58</v>
+        <v>795</v>
       </c>
       <c r="Q120" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
     </row>
     <row r="121" spans="1:17" ht="12.75">
       <c r="A121" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>215</v>
+        <v>84</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>216</v>
+        <v>181</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>217</v>
+        <v>85</v>
       </c>
       <c r="E121" s="3" t="s">
         <v>21</v>
@@ -7858,154 +7876,154 @@
         <v>23</v>
       </c>
       <c r="H121" s="5">
-        <v>2620089</v>
+        <v>2620444</v>
       </c>
       <c r="I121" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J121" s="3" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="K121" s="5">
         <v>2</v>
       </c>
       <c r="L121" s="5">
-        <v>1206</v>
+        <v>4905</v>
       </c>
       <c r="M121" s="3" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="N121" s="7">
-        <v>45943</v>
+        <v>46169</v>
       </c>
       <c r="O121" s="9">
-        <v>9360</v>
+        <v>795</v>
       </c>
       <c r="P121" s="9">
-        <v>3346.03</v>
+        <v>795</v>
       </c>
       <c r="Q121" s="3" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
     </row>
     <row r="122" spans="1:17" ht="12.75">
       <c r="A122" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H122" s="5">
+        <v>2620444</v>
+      </c>
+      <c r="I122" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J122" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="K122" s="5">
+        <v>3</v>
+      </c>
+      <c r="L122" s="5">
+        <v>4905</v>
+      </c>
+      <c r="M122" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="N122" s="7">
+        <v>46169</v>
+      </c>
+      <c r="O122" s="9">
+        <v>795</v>
+      </c>
+      <c r="P122" s="9">
+        <v>795</v>
+      </c>
+      <c r="Q122" s="3" t="s">
         <v>214</v>
-      </c>
-      <c r="B122" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="C122" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="D122" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F122" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G122" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H122" s="5">
-        <v>2620094</v>
-      </c>
-      <c r="I122" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J122" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="K122" s="5">
-        <v>1</v>
-      </c>
-      <c r="L122" s="5">
-        <v>1049</v>
-      </c>
-      <c r="M122" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="N122" s="7">
-        <v>45943</v>
-      </c>
-      <c r="O122" s="9">
-        <v>25000</v>
-      </c>
-      <c r="P122" s="9">
-        <v>19011.14</v>
-      </c>
-      <c r="Q122" s="3" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="123" spans="1:17" ht="12.75">
       <c r="A123" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>215</v>
+        <v>68</v>
       </c>
       <c r="C123" s="3" t="s">
         <v>216</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>217</v>
+        <v>69</v>
       </c>
       <c r="E123" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>22</v>
+        <v>192</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>23</v>
+        <v>193</v>
       </c>
       <c r="H123" s="5">
-        <v>2620095</v>
+        <v>2620382</v>
       </c>
       <c r="I123" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J123" s="3" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="K123" s="5">
         <v>1</v>
       </c>
       <c r="L123" s="5">
-        <v>1974</v>
+        <v>2968</v>
       </c>
       <c r="M123" s="3" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="N123" s="7">
-        <v>45943</v>
+        <v>46101</v>
       </c>
       <c r="O123" s="9">
-        <v>35000</v>
+        <v>18000</v>
       </c>
       <c r="P123" s="9">
-        <v>4819.64</v>
+        <v>10481.58</v>
       </c>
       <c r="Q123" s="3" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
     </row>
     <row r="124" spans="1:17" ht="12.75">
       <c r="A124" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E124" s="3" t="s">
         <v>21</v>
@@ -8017,48 +8035,48 @@
         <v>23</v>
       </c>
       <c r="H124" s="5">
-        <v>2620148</v>
+        <v>2620089</v>
       </c>
       <c r="I124" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J124" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K124" s="5">
         <v>1</v>
       </c>
       <c r="L124" s="5">
-        <v>1689</v>
+        <v>1206</v>
       </c>
       <c r="M124" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="N124" s="7">
+        <v>45943</v>
+      </c>
+      <c r="O124" s="9">
+        <v>2755.20</v>
+      </c>
+      <c r="P124" s="9">
+        <v>495.58</v>
+      </c>
+      <c r="Q124" s="3" t="s">
         <v>224</v>
-      </c>
-      <c r="N124" s="7">
-        <v>45947</v>
-      </c>
-      <c r="O124" s="9">
-        <v>34500</v>
-      </c>
-      <c r="P124" s="9">
-        <v>14.28</v>
-      </c>
-      <c r="Q124" s="3" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="125" spans="1:17" ht="12.75">
       <c r="A125" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E125" s="3" t="s">
         <v>21</v>
@@ -8070,48 +8088,48 @@
         <v>23</v>
       </c>
       <c r="H125" s="5">
-        <v>2620158</v>
+        <v>2620089</v>
       </c>
       <c r="I125" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J125" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K125" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L125" s="5">
-        <v>1464</v>
+        <v>1206</v>
       </c>
       <c r="M125" s="3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="N125" s="7">
-        <v>45952</v>
+        <v>45943</v>
       </c>
       <c r="O125" s="9">
-        <v>8000</v>
+        <v>9360</v>
       </c>
       <c r="P125" s="9">
-        <v>3247.29</v>
+        <v>2966.03</v>
       </c>
       <c r="Q125" s="3" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="126" spans="1:17" ht="12.75">
       <c r="A126" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="E126" s="3" t="s">
         <v>21</v>
@@ -8123,48 +8141,48 @@
         <v>23</v>
       </c>
       <c r="H126" s="5">
-        <v>2620159</v>
+        <v>2620094</v>
       </c>
       <c r="I126" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J126" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K126" s="5">
         <v>1</v>
       </c>
       <c r="L126" s="5">
-        <v>1464</v>
+        <v>1049</v>
       </c>
       <c r="M126" s="3" t="s">
         <v>225</v>
       </c>
       <c r="N126" s="7">
-        <v>45952</v>
+        <v>45943</v>
       </c>
       <c r="O126" s="9">
-        <v>75000</v>
+        <v>25000</v>
       </c>
       <c r="P126" s="9">
-        <v>21379.65</v>
+        <v>19011.14</v>
       </c>
       <c r="Q126" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="127" spans="1:17" ht="12.75">
       <c r="A127" s="3" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>149</v>
+        <v>219</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>151</v>
+        <v>221</v>
       </c>
       <c r="E127" s="3" t="s">
         <v>21</v>
@@ -8176,48 +8194,48 @@
         <v>23</v>
       </c>
       <c r="H127" s="5">
-        <v>2620093</v>
+        <v>2620095</v>
       </c>
       <c r="I127" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J127" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K127" s="5">
         <v>1</v>
       </c>
       <c r="L127" s="5">
-        <v>2106</v>
+        <v>1974</v>
       </c>
       <c r="M127" s="3" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="N127" s="7">
         <v>45943</v>
       </c>
       <c r="O127" s="9">
-        <v>3364.55</v>
+        <v>35000</v>
       </c>
       <c r="P127" s="9">
-        <v>0.01</v>
+        <v>4819.64</v>
       </c>
       <c r="Q127" s="3" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="128" spans="1:17" ht="12.75">
       <c r="A128" s="3" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>149</v>
+        <v>219</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>151</v>
+        <v>221</v>
       </c>
       <c r="E128" s="3" t="s">
         <v>21</v>
@@ -8229,48 +8247,48 @@
         <v>23</v>
       </c>
       <c r="H128" s="5">
-        <v>2620147</v>
+        <v>2620148</v>
       </c>
       <c r="I128" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J128" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K128" s="5">
         <v>1</v>
       </c>
       <c r="L128" s="5">
-        <v>2214</v>
+        <v>1689</v>
       </c>
       <c r="M128" s="3" t="s">
-        <v>162</v>
+        <v>228</v>
       </c>
       <c r="N128" s="7">
         <v>45947</v>
       </c>
       <c r="O128" s="9">
-        <v>4000</v>
+        <v>34500</v>
       </c>
       <c r="P128" s="9">
-        <v>438.69</v>
+        <v>14.28</v>
       </c>
       <c r="Q128" s="3" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
     </row>
     <row r="129" spans="1:17" ht="12.75">
       <c r="A129" s="3" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>149</v>
+        <v>219</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>151</v>
+        <v>221</v>
       </c>
       <c r="E129" s="3" t="s">
         <v>21</v>
@@ -8282,48 +8300,48 @@
         <v>23</v>
       </c>
       <c r="H129" s="5">
-        <v>2620249</v>
+        <v>2620158</v>
       </c>
       <c r="I129" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J129" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K129" s="5">
         <v>1</v>
       </c>
       <c r="L129" s="5">
-        <v>4921</v>
+        <v>1464</v>
       </c>
       <c r="M129" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="N129" s="7">
-        <v>45999</v>
+        <v>45952</v>
       </c>
       <c r="O129" s="9">
-        <v>13400</v>
+        <v>8000</v>
       </c>
       <c r="P129" s="9">
-        <v>1845.67</v>
+        <v>3078.23</v>
       </c>
       <c r="Q129" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="130" spans="1:17" ht="12.75">
       <c r="A130" s="3" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>149</v>
+        <v>219</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>151</v>
+        <v>221</v>
       </c>
       <c r="E130" s="3" t="s">
         <v>21</v>
@@ -8335,48 +8353,48 @@
         <v>23</v>
       </c>
       <c r="H130" s="5">
-        <v>2620379</v>
+        <v>2620159</v>
       </c>
       <c r="I130" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J130" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K130" s="5">
         <v>1</v>
       </c>
       <c r="L130" s="5">
-        <v>2214</v>
+        <v>1464</v>
       </c>
       <c r="M130" s="3" t="s">
-        <v>162</v>
+        <v>229</v>
       </c>
       <c r="N130" s="7">
-        <v>46098</v>
+        <v>45952</v>
       </c>
       <c r="O130" s="9">
-        <v>600</v>
+        <v>75000</v>
       </c>
       <c r="P130" s="9">
-        <v>600</v>
+        <v>21379.65</v>
       </c>
       <c r="Q130" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="131" spans="1:17" ht="12.75">
       <c r="A131" s="3" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E131" s="3" t="s">
         <v>21</v>
@@ -8388,48 +8406,48 @@
         <v>23</v>
       </c>
       <c r="H131" s="5">
-        <v>2620379</v>
+        <v>2620093</v>
       </c>
       <c r="I131" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J131" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K131" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L131" s="5">
-        <v>2214</v>
+        <v>2106</v>
       </c>
       <c r="M131" s="3" t="s">
-        <v>162</v>
+        <v>233</v>
       </c>
       <c r="N131" s="7">
-        <v>46098</v>
+        <v>45943</v>
       </c>
       <c r="O131" s="9">
-        <v>2476</v>
+        <v>3364.55</v>
       </c>
       <c r="P131" s="9">
-        <v>2476</v>
+        <v>0.01</v>
       </c>
       <c r="Q131" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="132" spans="1:17" ht="12.75">
       <c r="A132" s="3" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E132" s="3" t="s">
         <v>21</v>
@@ -8441,31 +8459,31 @@
         <v>23</v>
       </c>
       <c r="H132" s="5">
-        <v>2620379</v>
+        <v>2620147</v>
       </c>
       <c r="I132" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J132" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K132" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L132" s="5">
         <v>2214</v>
       </c>
       <c r="M132" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="N132" s="7">
-        <v>46098</v>
+        <v>45947</v>
       </c>
       <c r="O132" s="9">
-        <v>788.13</v>
+        <v>4000</v>
       </c>
       <c r="P132" s="9">
-        <v>314.12</v>
+        <v>438.69</v>
       </c>
       <c r="Q132" s="3" t="s">
         <v>235</v>
@@ -8473,16 +8491,16 @@
     </row>
     <row r="133" spans="1:17" ht="12.75">
       <c r="A133" s="3" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>68</v>
+        <v>153</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>69</v>
+        <v>155</v>
       </c>
       <c r="E133" s="3" t="s">
         <v>21</v>
@@ -8494,48 +8512,48 @@
         <v>23</v>
       </c>
       <c r="H133" s="5">
-        <v>2620090</v>
+        <v>2620249</v>
       </c>
       <c r="I133" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K133" s="5">
         <v>1</v>
       </c>
       <c r="L133" s="5">
-        <v>2018</v>
+        <v>4921</v>
       </c>
       <c r="M133" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="N133" s="7">
+        <v>45999</v>
+      </c>
+      <c r="O133" s="9">
+        <v>13400</v>
+      </c>
+      <c r="P133" s="9">
+        <v>1845.67</v>
+      </c>
+      <c r="Q133" s="3" t="s">
         <v>237</v>
-      </c>
-      <c r="N133" s="7">
-        <v>45943</v>
-      </c>
-      <c r="O133" s="9">
-        <v>9100</v>
-      </c>
-      <c r="P133" s="9">
-        <v>1487.50</v>
-      </c>
-      <c r="Q133" s="3" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="134" spans="1:17" ht="12.75">
       <c r="A134" s="3" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>68</v>
+        <v>153</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>69</v>
+        <v>155</v>
       </c>
       <c r="E134" s="3" t="s">
         <v>21</v>
@@ -8547,48 +8565,48 @@
         <v>23</v>
       </c>
       <c r="H134" s="5">
-        <v>2620146</v>
+        <v>2620379</v>
       </c>
       <c r="I134" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J134" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K134" s="5">
         <v>1</v>
       </c>
       <c r="L134" s="5">
-        <v>4767</v>
+        <v>2214</v>
       </c>
       <c r="M134" s="3" t="s">
-        <v>239</v>
+        <v>166</v>
       </c>
       <c r="N134" s="7">
-        <v>45947</v>
+        <v>46098</v>
       </c>
       <c r="O134" s="9">
-        <v>3600</v>
+        <v>600</v>
       </c>
       <c r="P134" s="9">
-        <v>2550</v>
+        <v>276.46</v>
       </c>
       <c r="Q134" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="135" spans="1:17" ht="12.75">
       <c r="A135" s="3" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>68</v>
+        <v>153</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>242</v>
+        <v>220</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>69</v>
+        <v>155</v>
       </c>
       <c r="E135" s="3" t="s">
         <v>21</v>
@@ -8600,310 +8618,310 @@
         <v>23</v>
       </c>
       <c r="H135" s="5">
-        <v>2620255</v>
+        <v>2620379</v>
       </c>
       <c r="I135" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J135" s="3" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="K135" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L135" s="5">
-        <v>2147</v>
+        <v>2214</v>
       </c>
       <c r="M135" s="3" t="s">
-        <v>244</v>
+        <v>166</v>
       </c>
       <c r="N135" s="7">
-        <v>46000</v>
+        <v>46098</v>
       </c>
       <c r="O135" s="9">
-        <v>30000</v>
+        <v>2476</v>
       </c>
       <c r="P135" s="9">
-        <v>7500</v>
+        <v>2476</v>
       </c>
       <c r="Q135" s="3" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
     </row>
     <row r="136" spans="1:17" ht="12.75">
       <c r="A136" s="3" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>247</v>
+        <v>153</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>248</v>
+        <v>220</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>249</v>
+        <v>155</v>
       </c>
       <c r="E136" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>250</v>
+        <v>22</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>251</v>
+        <v>23</v>
       </c>
       <c r="H136" s="5">
-        <v>2620295</v>
+        <v>2620379</v>
       </c>
       <c r="I136" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J136" s="3" t="s">
-        <v>252</v>
+        <v>222</v>
       </c>
       <c r="K136" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L136" s="5">
-        <v>3985</v>
+        <v>2214</v>
       </c>
       <c r="M136" s="3" t="s">
-        <v>253</v>
+        <v>166</v>
       </c>
       <c r="N136" s="7">
-        <v>46030</v>
+        <v>46098</v>
       </c>
       <c r="O136" s="9">
-        <v>10000</v>
+        <v>788.13</v>
       </c>
       <c r="P136" s="9">
-        <v>2611.86</v>
+        <v>314.12</v>
       </c>
       <c r="Q136" s="3" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
     </row>
     <row r="137" spans="1:17" ht="12.75">
       <c r="A137" s="3" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>247</v>
+        <v>153</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>248</v>
+        <v>220</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>249</v>
+        <v>155</v>
       </c>
       <c r="E137" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>250</v>
+        <v>22</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>251</v>
+        <v>23</v>
       </c>
       <c r="H137" s="5">
-        <v>2620295</v>
+        <v>2620497</v>
       </c>
       <c r="I137" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J137" s="3" t="s">
-        <v>252</v>
+        <v>222</v>
       </c>
       <c r="K137" s="5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L137" s="5">
-        <v>3985</v>
+        <v>5086</v>
       </c>
       <c r="M137" s="3" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="N137" s="7">
-        <v>46030</v>
+        <v>46224</v>
       </c>
       <c r="O137" s="9">
-        <v>21000</v>
+        <v>675</v>
       </c>
       <c r="P137" s="9">
-        <v>8291.88</v>
+        <v>675</v>
       </c>
       <c r="Q137" s="3" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
     </row>
     <row r="138" spans="1:17" ht="12.75">
       <c r="A138" s="3" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>247</v>
+        <v>153</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>248</v>
+        <v>220</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>249</v>
+        <v>155</v>
       </c>
       <c r="E138" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>250</v>
+        <v>22</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>251</v>
+        <v>23</v>
       </c>
       <c r="H138" s="5">
-        <v>2620327</v>
+        <v>2620497</v>
       </c>
       <c r="I138" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J138" s="3" t="s">
-        <v>256</v>
+        <v>222</v>
       </c>
       <c r="K138" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L138" s="5">
-        <v>1650</v>
+        <v>5086</v>
       </c>
       <c r="M138" s="3" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="N138" s="7">
-        <v>46057</v>
+        <v>46224</v>
       </c>
       <c r="O138" s="9">
-        <v>12000</v>
+        <v>241.18</v>
       </c>
       <c r="P138" s="9">
-        <v>5700</v>
+        <v>241.18</v>
       </c>
       <c r="Q138" s="3" t="s">
-        <v>258</v>
+        <v>242</v>
       </c>
     </row>
     <row r="139" spans="1:17" ht="12.75">
       <c r="A139" s="3" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>247</v>
+        <v>153</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>248</v>
+        <v>220</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>249</v>
+        <v>155</v>
       </c>
       <c r="E139" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>250</v>
+        <v>22</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>251</v>
+        <v>23</v>
       </c>
       <c r="H139" s="5">
-        <v>2620327</v>
+        <v>2620497</v>
       </c>
       <c r="I139" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J139" s="3" t="s">
-        <v>256</v>
+        <v>222</v>
       </c>
       <c r="K139" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L139" s="5">
-        <v>1650</v>
+        <v>5086</v>
       </c>
       <c r="M139" s="3" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="N139" s="7">
-        <v>46057</v>
+        <v>46224</v>
       </c>
       <c r="O139" s="9">
-        <v>6900</v>
+        <v>100</v>
       </c>
       <c r="P139" s="9">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="Q139" s="3" t="s">
-        <v>259</v>
+        <v>243</v>
       </c>
     </row>
     <row r="140" spans="1:17" ht="12.75">
       <c r="A140" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G140" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H140" s="5">
+        <v>2620090</v>
+      </c>
+      <c r="I140" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J140" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="K140" s="5">
+        <v>1</v>
+      </c>
+      <c r="L140" s="5">
+        <v>2018</v>
+      </c>
+      <c r="M140" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="N140" s="7">
+        <v>45943</v>
+      </c>
+      <c r="O140" s="9">
+        <v>9100</v>
+      </c>
+      <c r="P140" s="9">
+        <v>1487.50</v>
+      </c>
+      <c r="Q140" s="3" t="s">
         <v>246</v>
-      </c>
-      <c r="B140" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C140" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D140" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E140" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F140" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G140" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="H140" s="5">
-        <v>2620327</v>
-      </c>
-      <c r="I140" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J140" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="K140" s="5">
-        <v>3</v>
-      </c>
-      <c r="L140" s="5">
-        <v>1650</v>
-      </c>
-      <c r="M140" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="N140" s="7">
-        <v>46057</v>
-      </c>
-      <c r="O140" s="9">
-        <v>8925</v>
-      </c>
-      <c r="P140" s="9">
-        <v>2975</v>
-      </c>
-      <c r="Q140" s="3" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="141" spans="1:17" ht="12.75">
       <c r="A141" s="3" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>248</v>
+        <v>220</v>
       </c>
       <c r="D141" s="3" t="s">
         <v>69</v>
@@ -8912,51 +8930,51 @@
         <v>21</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>250</v>
+        <v>22</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>251</v>
+        <v>23</v>
       </c>
       <c r="H141" s="5">
-        <v>2620475</v>
+        <v>2620146</v>
       </c>
       <c r="I141" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J141" s="3" t="s">
-        <v>256</v>
+        <v>222</v>
       </c>
       <c r="K141" s="5">
         <v>1</v>
       </c>
       <c r="L141" s="5">
-        <v>5204</v>
+        <v>4767</v>
       </c>
       <c r="M141" s="3" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="N141" s="7">
-        <v>46204</v>
+        <v>45947</v>
       </c>
       <c r="O141" s="9">
-        <v>4990</v>
+        <v>3600</v>
       </c>
       <c r="P141" s="9">
-        <v>2495</v>
+        <v>2550</v>
       </c>
       <c r="Q141" s="3" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
     </row>
     <row r="142" spans="1:17" ht="12.75">
       <c r="A142" s="3" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>68</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D142" s="3" t="s">
         <v>69</v>
@@ -8965,372 +8983,372 @@
         <v>21</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>250</v>
+        <v>22</v>
       </c>
       <c r="G142" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H142" s="5">
+        <v>2620255</v>
+      </c>
+      <c r="I142" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J142" s="3" t="s">
         <v>251</v>
-      </c>
-      <c r="H142" s="5">
-        <v>2620493</v>
-      </c>
-      <c r="I142" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J142" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="K142" s="5">
         <v>1</v>
       </c>
       <c r="L142" s="5">
-        <v>1398</v>
+        <v>2147</v>
       </c>
       <c r="M142" s="3" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="N142" s="7">
-        <v>46223</v>
+        <v>46000</v>
       </c>
       <c r="O142" s="9">
-        <v>5640</v>
+        <v>30000</v>
       </c>
       <c r="P142" s="9">
-        <v>5640</v>
+        <v>7500</v>
       </c>
       <c r="Q142" s="3" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
     </row>
     <row r="143" spans="1:17" ht="12.75">
       <c r="A143" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F143" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="H143" s="5">
+        <v>2620295</v>
+      </c>
+      <c r="I143" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J143" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="B143" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C143" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D143" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E143" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F143" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G143" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="H143" s="5">
-        <v>2620493</v>
-      </c>
-      <c r="I143" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J143" s="3" t="s">
-        <v>256</v>
-      </c>
       <c r="K143" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L143" s="5">
-        <v>1398</v>
+        <v>3985</v>
       </c>
       <c r="M143" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="N143" s="7">
-        <v>46223</v>
+        <v>46030</v>
       </c>
       <c r="O143" s="9">
-        <v>722</v>
+        <v>10000</v>
       </c>
       <c r="P143" s="9">
-        <v>722</v>
+        <v>2611.86</v>
       </c>
       <c r="Q143" s="3" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="144" spans="1:17" ht="12.75">
       <c r="A144" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="H144" s="5">
+        <v>2620295</v>
+      </c>
+      <c r="I144" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J144" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="B144" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C144" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D144" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E144" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F144" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G144" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="H144" s="5">
-        <v>2620493</v>
-      </c>
-      <c r="I144" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J144" s="3" t="s">
-        <v>256</v>
-      </c>
       <c r="K144" s="5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L144" s="5">
-        <v>1398</v>
+        <v>3985</v>
       </c>
       <c r="M144" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="N144" s="7">
+        <v>46030</v>
+      </c>
+      <c r="O144" s="9">
+        <v>21000</v>
+      </c>
+      <c r="P144" s="9">
+        <v>8291.88</v>
+      </c>
+      <c r="Q144" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="N144" s="7">
-        <v>46223</v>
-      </c>
-      <c r="O144" s="9">
-        <v>450</v>
-      </c>
-      <c r="P144" s="9">
-        <v>450</v>
-      </c>
-      <c r="Q144" s="3" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="145" spans="1:17" ht="12.75">
       <c r="A145" s="3" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="E145" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>22</v>
+        <v>258</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>23</v>
+        <v>259</v>
       </c>
       <c r="H145" s="5">
-        <v>2620051</v>
+        <v>2620327</v>
       </c>
       <c r="I145" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J145" s="3" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="K145" s="5">
         <v>1</v>
       </c>
       <c r="L145" s="5">
-        <v>4906</v>
+        <v>1650</v>
       </c>
       <c r="M145" s="3" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="N145" s="7">
-        <v>45933</v>
+        <v>46057</v>
       </c>
       <c r="O145" s="9">
-        <v>20000</v>
+        <v>12000</v>
       </c>
       <c r="P145" s="9">
-        <v>3871.33</v>
+        <v>5700</v>
       </c>
       <c r="Q145" s="3" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
     </row>
     <row r="146" spans="1:17" ht="12.75">
       <c r="A146" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="H146" s="5">
+        <v>2620327</v>
+      </c>
+      <c r="I146" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J146" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="K146" s="5">
+        <v>2</v>
+      </c>
+      <c r="L146" s="5">
+        <v>1650</v>
+      </c>
+      <c r="M146" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="N146" s="7">
+        <v>46057</v>
+      </c>
+      <c r="O146" s="9">
+        <v>6900</v>
+      </c>
+      <c r="P146" s="9">
+        <v>600</v>
+      </c>
+      <c r="Q146" s="3" t="s">
         <v>267</v>
-      </c>
-      <c r="B146" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="C146" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="D146" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="E146" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F146" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G146" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H146" s="5">
-        <v>2620152</v>
-      </c>
-      <c r="I146" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J146" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="K146" s="5">
-        <v>1</v>
-      </c>
-      <c r="L146" s="5">
-        <v>1954</v>
-      </c>
-      <c r="M146" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="N146" s="7">
-        <v>45950</v>
-      </c>
-      <c r="O146" s="9">
-        <v>40000</v>
-      </c>
-      <c r="P146" s="9">
-        <v>20087.50</v>
-      </c>
-      <c r="Q146" s="3" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="147" spans="1:17" ht="12.75">
       <c r="A147" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>268</v>
+        <v>68</v>
       </c>
       <c r="C147" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F147" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="G147" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="H147" s="5">
+        <v>2620475</v>
+      </c>
+      <c r="I147" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J147" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="K147" s="5">
+        <v>1</v>
+      </c>
+      <c r="L147" s="5">
+        <v>5204</v>
+      </c>
+      <c r="M147" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D147" s="3" t="s">
+      <c r="N147" s="7">
+        <v>46204</v>
+      </c>
+      <c r="O147" s="9">
+        <v>4990</v>
+      </c>
+      <c r="P147" s="9">
+        <v>2495</v>
+      </c>
+      <c r="Q147" s="3" t="s">
         <v>270</v>
-      </c>
-      <c r="E147" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F147" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G147" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H147" s="5">
-        <v>2620284</v>
-      </c>
-      <c r="I147" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J147" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="K147" s="5">
-        <v>3</v>
-      </c>
-      <c r="L147" s="5">
-        <v>3099</v>
-      </c>
-      <c r="M147" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="N147" s="7">
-        <v>46028</v>
-      </c>
-      <c r="O147" s="9">
-        <v>13210.50</v>
-      </c>
-      <c r="P147" s="9">
-        <v>777.75</v>
-      </c>
-      <c r="Q147" s="3" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="148" spans="1:17" ht="12.75">
       <c r="A148" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>268</v>
+        <v>68</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>270</v>
+        <v>69</v>
       </c>
       <c r="E148" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>22</v>
+        <v>258</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>23</v>
+        <v>259</v>
       </c>
       <c r="H148" s="5">
-        <v>2620284</v>
+        <v>2620493</v>
       </c>
       <c r="I148" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J148" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="K148" s="5">
+        <v>1</v>
+      </c>
+      <c r="L148" s="5">
+        <v>1398</v>
+      </c>
+      <c r="M148" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="K148" s="5">
-        <v>4</v>
-      </c>
-      <c r="L148" s="5">
-        <v>3099</v>
-      </c>
-      <c r="M148" s="3" t="s">
-        <v>276</v>
-      </c>
       <c r="N148" s="7">
-        <v>46028</v>
+        <v>46223</v>
       </c>
       <c r="O148" s="9">
-        <v>4000</v>
+        <v>5640</v>
       </c>
       <c r="P148" s="9">
-        <v>4000</v>
+        <v>3760</v>
       </c>
       <c r="Q148" s="3" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
     </row>
     <row r="149" spans="1:17" ht="12.75">
       <c r="A149" s="3" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E149" s="3" t="s">
         <v>21</v>
@@ -9342,48 +9360,48 @@
         <v>23</v>
       </c>
       <c r="H149" s="5">
-        <v>2620420</v>
+        <v>2620051</v>
       </c>
       <c r="I149" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J149" s="3" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="K149" s="5">
         <v>1</v>
       </c>
       <c r="L149" s="5">
-        <v>1465</v>
+        <v>4906</v>
       </c>
       <c r="M149" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="N149" s="7">
-        <v>46143</v>
+        <v>45933</v>
       </c>
       <c r="O149" s="9">
-        <v>29117</v>
+        <v>20000</v>
       </c>
       <c r="P149" s="9">
-        <v>29117</v>
+        <v>3871.33</v>
       </c>
       <c r="Q149" s="3" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="150" spans="1:17" ht="12.75">
       <c r="A150" s="3" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="B150" s="3" t="s">
-        <v>68</v>
+        <v>274</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>69</v>
+        <v>276</v>
       </c>
       <c r="E150" s="3" t="s">
         <v>21</v>
@@ -9395,48 +9413,48 @@
         <v>23</v>
       </c>
       <c r="H150" s="5">
-        <v>2620296</v>
+        <v>2620152</v>
       </c>
       <c r="I150" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J150" s="3" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="K150" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L150" s="5">
-        <v>3739</v>
+        <v>1954</v>
       </c>
       <c r="M150" s="3" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="N150" s="7">
-        <v>46034</v>
+        <v>45950</v>
       </c>
       <c r="O150" s="9">
-        <v>5336</v>
+        <v>40000</v>
       </c>
       <c r="P150" s="9">
-        <v>1509.50</v>
+        <v>20087.50</v>
       </c>
       <c r="Q150" s="3" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
     </row>
     <row r="151" spans="1:17" ht="12.75">
       <c r="A151" s="3" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="E151" s="3" t="s">
         <v>21</v>
@@ -9448,48 +9466,48 @@
         <v>23</v>
       </c>
       <c r="H151" s="5">
-        <v>2620061</v>
+        <v>2620284</v>
       </c>
       <c r="I151" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J151" s="3" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="K151" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L151" s="5">
-        <v>4918</v>
+        <v>3099</v>
       </c>
       <c r="M151" s="3" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="N151" s="7">
-        <v>45933</v>
+        <v>46028</v>
       </c>
       <c r="O151" s="9">
-        <v>5963</v>
+        <v>13210.50</v>
       </c>
       <c r="P151" s="9">
-        <v>355</v>
+        <v>777.75</v>
       </c>
       <c r="Q151" s="3" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
     </row>
     <row r="152" spans="1:17" ht="12.75">
       <c r="A152" s="3" t="s">
-        <v>292</v>
+        <v>273</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>294</v>
+        <v>275</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>295</v>
+        <v>276</v>
       </c>
       <c r="E152" s="3" t="s">
         <v>21</v>
@@ -9501,48 +9519,48 @@
         <v>23</v>
       </c>
       <c r="H152" s="5">
-        <v>2620050</v>
+        <v>2620284</v>
       </c>
       <c r="I152" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J152" s="3" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="K152" s="5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L152" s="5">
-        <v>1417</v>
+        <v>3099</v>
       </c>
       <c r="M152" s="3" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="N152" s="7">
-        <v>45933</v>
+        <v>46028</v>
       </c>
       <c r="O152" s="9">
-        <v>1873</v>
+        <v>4000</v>
       </c>
       <c r="P152" s="9">
-        <v>362.47</v>
+        <v>4000</v>
       </c>
       <c r="Q152" s="3" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
     </row>
     <row r="153" spans="1:17" ht="12.75">
       <c r="A153" s="3" t="s">
-        <v>298</v>
+        <v>285</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="E153" s="3" t="s">
         <v>21</v>
@@ -9554,48 +9572,48 @@
         <v>23</v>
       </c>
       <c r="H153" s="5">
-        <v>2620153</v>
+        <v>2620420</v>
       </c>
       <c r="I153" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J153" s="3" t="s">
-        <v>301</v>
+        <v>277</v>
       </c>
       <c r="K153" s="5">
         <v>1</v>
       </c>
       <c r="L153" s="5">
-        <v>1755</v>
+        <v>1465</v>
       </c>
       <c r="M153" s="3" t="s">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="N153" s="7">
-        <v>45950</v>
+        <v>46143</v>
       </c>
       <c r="O153" s="9">
-        <v>10000</v>
+        <v>29117</v>
       </c>
       <c r="P153" s="9">
-        <v>3623</v>
+        <v>29117</v>
       </c>
       <c r="Q153" s="3" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
     </row>
     <row r="154" spans="1:17" ht="12.75">
       <c r="A154" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>299</v>
+        <v>68</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>300</v>
+        <v>69</v>
       </c>
       <c r="E154" s="3" t="s">
         <v>21</v>
@@ -9607,48 +9625,48 @@
         <v>23</v>
       </c>
       <c r="H154" s="5">
-        <v>2620492</v>
+        <v>2620296</v>
       </c>
       <c r="I154" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J154" s="3" t="s">
-        <v>301</v>
+        <v>277</v>
       </c>
       <c r="K154" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L154" s="5">
-        <v>1071</v>
+        <v>3739</v>
       </c>
       <c r="M154" s="3" t="s">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="N154" s="7">
-        <v>46223</v>
+        <v>46034</v>
       </c>
       <c r="O154" s="9">
-        <v>434</v>
+        <v>5336</v>
       </c>
       <c r="P154" s="9">
-        <v>434</v>
+        <v>1509.50</v>
       </c>
       <c r="Q154" s="3" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
     </row>
     <row r="155" spans="1:17" ht="12.75">
       <c r="A155" s="3" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="E155" s="3" t="s">
         <v>21</v>
@@ -9660,48 +9678,48 @@
         <v>23</v>
       </c>
       <c r="H155" s="5">
-        <v>2620495</v>
+        <v>2620061</v>
       </c>
       <c r="I155" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J155" s="3" t="s">
-        <v>301</v>
+        <v>277</v>
       </c>
       <c r="K155" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L155" s="5">
-        <v>1071</v>
+        <v>4918</v>
       </c>
       <c r="M155" s="3" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="N155" s="7">
-        <v>46223</v>
+        <v>45933</v>
       </c>
       <c r="O155" s="9">
-        <v>3852</v>
+        <v>5963</v>
       </c>
       <c r="P155" s="9">
-        <v>3852</v>
+        <v>355</v>
       </c>
       <c r="Q155" s="3" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
     </row>
     <row r="156" spans="1:17" ht="12.75">
       <c r="A156" s="3" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>269</v>
+        <v>300</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="E156" s="3" t="s">
         <v>21</v>
@@ -9713,48 +9731,48 @@
         <v>23</v>
       </c>
       <c r="H156" s="5">
-        <v>2620176</v>
+        <v>2620050</v>
       </c>
       <c r="I156" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J156" s="3" t="s">
-        <v>301</v>
+        <v>277</v>
       </c>
       <c r="K156" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L156" s="5">
-        <v>1216</v>
+        <v>1417</v>
       </c>
       <c r="M156" s="3" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="N156" s="7">
-        <v>45960</v>
+        <v>45933</v>
       </c>
       <c r="O156" s="9">
-        <v>10700</v>
+        <v>1873</v>
       </c>
       <c r="P156" s="9">
-        <v>2675</v>
+        <v>362.47</v>
       </c>
       <c r="Q156" s="3" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
     </row>
     <row r="157" spans="1:17" ht="12.75">
       <c r="A157" s="3" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="E157" s="3" t="s">
         <v>21</v>
@@ -9766,34 +9784,246 @@
         <v>23</v>
       </c>
       <c r="H157" s="5">
-        <v>2620496</v>
+        <v>2620153</v>
       </c>
       <c r="I157" s="3" t="s">
         <v>24</v>
       </c>
       <c r="J157" s="3" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="K157" s="5">
         <v>1</v>
       </c>
       <c r="L157" s="5">
+        <v>1755</v>
+      </c>
+      <c r="M157" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="N157" s="7">
+        <v>45950</v>
+      </c>
+      <c r="O157" s="9">
+        <v>10000</v>
+      </c>
+      <c r="P157" s="9">
+        <v>3623</v>
+      </c>
+      <c r="Q157" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="158" spans="1:17" ht="12.75">
+      <c r="A158" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="E158" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F158" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G158" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H158" s="5">
+        <v>2620492</v>
+      </c>
+      <c r="I158" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J158" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="K158" s="5">
+        <v>1</v>
+      </c>
+      <c r="L158" s="5">
+        <v>1071</v>
+      </c>
+      <c r="M158" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="N158" s="7">
+        <v>46223</v>
+      </c>
+      <c r="O158" s="9">
+        <v>434</v>
+      </c>
+      <c r="P158" s="9">
+        <v>434</v>
+      </c>
+      <c r="Q158" s="3" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="159" spans="1:17" ht="12.75">
+      <c r="A159" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="E159" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F159" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G159" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H159" s="5">
+        <v>2620495</v>
+      </c>
+      <c r="I159" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J159" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="K159" s="5">
+        <v>1</v>
+      </c>
+      <c r="L159" s="5">
+        <v>1071</v>
+      </c>
+      <c r="M159" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="N159" s="7">
+        <v>46223</v>
+      </c>
+      <c r="O159" s="9">
+        <v>3852</v>
+      </c>
+      <c r="P159" s="9">
+        <v>3852</v>
+      </c>
+      <c r="Q159" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="160" spans="1:17" ht="12.75">
+      <c r="A160" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="E160" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F160" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G160" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H160" s="5">
+        <v>2620176</v>
+      </c>
+      <c r="I160" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J160" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="K160" s="5">
+        <v>4</v>
+      </c>
+      <c r="L160" s="5">
+        <v>1216</v>
+      </c>
+      <c r="M160" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="N160" s="7">
+        <v>45960</v>
+      </c>
+      <c r="O160" s="9">
+        <v>10700</v>
+      </c>
+      <c r="P160" s="9">
+        <v>2675</v>
+      </c>
+      <c r="Q160" s="3" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="161" spans="1:17" ht="12.75">
+      <c r="A161" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F161" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G161" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H161" s="5">
+        <v>2620496</v>
+      </c>
+      <c r="I161" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J161" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="K161" s="5">
+        <v>1</v>
+      </c>
+      <c r="L161" s="5">
         <v>5090</v>
       </c>
-      <c r="M157" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="N157" s="7">
+      <c r="M161" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="N161" s="7">
         <v>46223</v>
       </c>
-      <c r="O157" s="9">
+      <c r="O161" s="9">
         <v>3867</v>
       </c>
-      <c r="P157" s="9">
+      <c r="P161" s="9">
         <v>3867</v>
       </c>
-      <c r="Q157" s="3" t="s">
-        <v>316</v>
+      <c r="Q161" s="3" t="s">
+        <v>322</v>
       </c>
     </row>
   </sheetData>
